--- a/artfynd/A 39150-2024 artfynd.xlsx
+++ b/artfynd/A 39150-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,121 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130669698</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58284</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lidbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>613692</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6943970</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39150-2024 artfynd.xlsx
+++ b/artfynd/A 39150-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130669698</v>
       </c>
       <c r="B3" t="n">
-        <v>58284</v>
+        <v>58286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39150-2024 artfynd.xlsx
+++ b/artfynd/A 39150-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130669698</v>
       </c>
       <c r="B3" t="n">
-        <v>58286</v>
+        <v>58294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39150-2024 artfynd.xlsx
+++ b/artfynd/A 39150-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130669698</v>
       </c>
       <c r="B3" t="n">
-        <v>58294</v>
+        <v>58295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39150-2024 artfynd.xlsx
+++ b/artfynd/A 39150-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130669698</v>
       </c>
       <c r="B3" t="n">
-        <v>58295</v>
+        <v>58296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39150-2024 artfynd.xlsx
+++ b/artfynd/A 39150-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 39150-2024 artfynd.xlsx
+++ b/artfynd/A 39150-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
